--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128828402</v>
       </c>
       <c r="B2" t="n">
-        <v>91478</v>
+        <v>91483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128828178</v>
       </c>
       <c r="B3" t="n">
-        <v>92123</v>
+        <v>92128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128828402</v>
       </c>
       <c r="B2" t="n">
-        <v>91483</v>
+        <v>91488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128828178</v>
       </c>
       <c r="B3" t="n">
-        <v>92128</v>
+        <v>92133</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128828402</v>
       </c>
       <c r="B2" t="n">
-        <v>91488</v>
+        <v>91492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128828178</v>
       </c>
       <c r="B3" t="n">
-        <v>92133</v>
+        <v>92137</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128828402</v>
       </c>
       <c r="B2" t="n">
-        <v>91492</v>
+        <v>91497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128828178</v>
       </c>
       <c r="B3" t="n">
-        <v>92137</v>
+        <v>92142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128828402</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128828178</v>
       </c>
       <c r="B3" t="n">
-        <v>92150</v>
+        <v>92155</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128828402</v>
       </c>
       <c r="B2" t="n">
-        <v>91507</v>
+        <v>91510</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128828178</v>
       </c>
       <c r="B3" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128828402</v>
       </c>
       <c r="B2" t="n">
-        <v>91510</v>
+        <v>91517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128828178</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92165</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128828402</v>
       </c>
       <c r="B2" t="n">
-        <v>91517</v>
+        <v>91524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128828178</v>
       </c>
       <c r="B3" t="n">
-        <v>92165</v>
+        <v>92172</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128828402</v>
       </c>
       <c r="B2" t="n">
-        <v>91524</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128828178</v>
       </c>
       <c r="B3" t="n">
-        <v>92172</v>
+        <v>92174</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128828402</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>91524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128828178</v>
       </c>
       <c r="B3" t="n">
-        <v>92174</v>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>128828178</v>
       </c>
       <c r="B3" t="n">
-        <v>92189</v>
+        <v>92190</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26757-2025 artfynd.xlsx
+++ b/artfynd/A 26757-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128828402</v>
+        <v>128828178</v>
       </c>
       <c r="B2" t="n">
-        <v>91524</v>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,24 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4660</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -717,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397436</v>
+        <v>397493</v>
       </c>
       <c r="R2" t="n">
-        <v>6639542</v>
+        <v>6639535</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -752,7 +756,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,12 +766,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Fruktkroppar från fjolåret på högstubbe av asp</t>
+          <t>På tre olika lågor av gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128828178</v>
+        <v>128828402</v>
       </c>
       <c r="B3" t="n">
-        <v>92190</v>
+        <v>91893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,28 +809,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>4660</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397493</v>
+        <v>397436</v>
       </c>
       <c r="R3" t="n">
-        <v>6639535</v>
+        <v>6639542</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På tre olika lågor av gran</t>
+          <t>Fruktkroppar från fjolåret på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,6 +914,114 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>111919018</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91966</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Askerudsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>397508</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6639553</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Björk, Martin Eneling, Jonas Göransson, Johanna Klauss, Edvin Johansson , Amanda Evensen, Olavi Niemelä, Agnes Rengren, August Oljeqvist, Åsa Röstell, Kim Ohlsson , Daniel Hertz Wallin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
